--- a/AAII_Financials/Yearly/CGNT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CGNT_YR_FIN.xlsx
@@ -2707,7 +2707,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5400</v>
+        <v>5700</v>
       </c>
       <c r="E58" s="3">
         <v>5000</v>
@@ -2752,7 +2752,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>111300</v>
+        <v>110900</v>
       </c>
       <c r="E59" s="3">
         <v>117100</v>
